--- a/04-planning/springs/Planning Mesa de Servicio - 2026.xlsx
+++ b/04-planning/springs/Planning Mesa de Servicio - 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA87E0E-7AA6-4096-8A5B-138791BBDEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFB51C1-3EAE-4A22-8D5F-C6097A715216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Draft" sheetId="1" state="hidden" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="474">
   <si>
     <t>Stages</t>
   </si>
@@ -417,7 +417,7 @@
     <t>Total horas estimadas (Julio)</t>
   </si>
   <si>
-    <t>AGOSTO · Diseño del Servicio Autónomo e Inteligente (N5) — Definir el modelo operativo óptimo, alinear expectativas con comercial y pilotar herramientas</t>
+    <t>AGOSTO · Diseño del Servicio Autónomo e Inteligente (N5) — modelo operativo, herramientas, validación comercial</t>
   </si>
   <si>
     <t>E2-HU001</t>
@@ -450,7 +450,7 @@
     <t>033. Definir modelo de operación híbrido: agente IA + humano por nivel</t>
   </si>
   <si>
-    <t>Modelo de operación híbrido documentado: qué hace la IA y qué hace el humano en cada nivel</t>
+    <t>Modelo de operación híbrido: qué hace la IA y qué hace el humano en cada nivel</t>
   </si>
   <si>
     <t>E2-005</t>
@@ -465,7 +465,7 @@
     <t>E2-006</t>
   </si>
   <si>
-    <t>035. Definir roles + RACI por nivel N1/N2/N3 (Coordinador, Líder Técnico, Especialista)</t>
+    <t>035. Definir roles + RACI por nivel N1/N2/N3</t>
   </si>
   <si>
     <t>RACI documentado por nivel con responsabilidades claras por rol</t>
@@ -480,6 +480,114 @@
     <t>Lineamiento KEDB + diseño del portal N0 de autoservicio</t>
   </si>
   <si>
+    <t>E2-HU002</t>
+  </si>
+  <si>
+    <t>E2 [HU-002] - Alineación de expectativas del servicio nuevo con comercial y operación</t>
+  </si>
+  <si>
+    <t>E2-010</t>
+  </si>
+  <si>
+    <t>038. Diseñar slide deck comercial: value proposition, dolores, modelo y diferenciador PS</t>
+  </si>
+  <si>
+    <t>Slide deck comercial v1.0 listo para presentar a clientes nuevos</t>
+  </si>
+  <si>
+    <t>E2-011</t>
+  </si>
+  <si>
+    <t>039. Diseñar slide deck para equipo de operación: qué cambia, roles y proceso de recepción</t>
+  </si>
+  <si>
+    <t>Slide deck de operación v1.0: cómo recibir y ejecutar el servicio</t>
+  </si>
+  <si>
+    <t>E2-013</t>
+  </si>
+  <si>
+    <t>040. Validación y feedback de las definiciones del servicio con comercial y DMs</t>
+  </si>
+  <si>
+    <t>Acta de validación y ajustes acordados con equipo comercial</t>
+  </si>
+  <si>
+    <t>E2-014</t>
+  </si>
+  <si>
+    <t>041. Validar modelo operativo con líderes de operación (trenes)</t>
+  </si>
+  <si>
+    <t>Acta de validación con líderes de operación y ajustes incorporados</t>
+  </si>
+  <si>
+    <t>E2-HU004</t>
+  </si>
+  <si>
+    <t>E2 [HU-004] - Piloto herramientas y agentes para las mesas de servicio</t>
+  </si>
+  <si>
+    <t>E2-019</t>
+  </si>
+  <si>
+    <t>042. Evaluar y seleccionar herramienta estándar PersonalSoft para gestión de tickets</t>
+  </si>
+  <si>
+    <t>Decisión documentada: herramienta estándar PS seleccionada con criterios y justificación</t>
+  </si>
+  <si>
+    <t>E2-020</t>
+  </si>
+  <si>
+    <t>043. Identificar y priorizar automatizaciones: agentes IA y robots RPA para el servicio</t>
+  </si>
+  <si>
+    <t>Inventario priorizado de automatizaciones con caso de uso por nivel</t>
+  </si>
+  <si>
+    <t>E2-021</t>
+  </si>
+  <si>
+    <t>044. Diseñar e iniciar piloto de herramientas/agentes para las mesas (reuso o construcción nueva)</t>
+  </si>
+  <si>
+    <t>Piloto de herramientas/agentes diseñado y en ejecución con resultados preliminares</t>
+  </si>
+  <si>
+    <t>E2-022</t>
+  </si>
+  <si>
+    <t>045. Diseñar estructura de reportes ejecutivos y dashboard de operación para PS</t>
+  </si>
+  <si>
+    <t>Diseño del dashboard ejecutivo interno PS: métricas, frecuencia y responsables</t>
+  </si>
+  <si>
+    <t>E2-024</t>
+  </si>
+  <si>
+    <t>046. Definir lineamientos de gestión de conocimiento y límites del servicio por tipo de mesa</t>
+  </si>
+  <si>
+    <t>Lineamiento de límites del servicio + guía de gestión del conocimiento por tipo de mesa</t>
+  </si>
+  <si>
+    <t>Total horas estimadas (Agosto)</t>
+  </si>
+  <si>
+    <t>SEPTIEMBRE · Productización → Piloto Cliente Nuevo → inicio del Lanzamiento (sin lanzamiento oficial que va a Octubre)</t>
+  </si>
+  <si>
+    <t>E3-HU001</t>
+  </si>
+  <si>
+    <t>E3 [HU-001] - Productización del servicio: colaterales, calculadora y habilitaciones</t>
+  </si>
+  <si>
+    <t>Productización del Servicio</t>
+  </si>
+  <si>
     <t>E2-009</t>
   </si>
   <si>
@@ -489,118 +597,10 @@
     <t>Calculadora FTE v1.0 con modelo de GAP administrativo y parámetros clave</t>
   </si>
   <si>
-    <t>E2-HU002</t>
-  </si>
-  <si>
-    <t>E2 [HU-002] - Alineación de expectativas del servicio nuevo con comercial y operación</t>
-  </si>
-  <si>
-    <t>E2-010</t>
-  </si>
-  <si>
-    <t>038. Diseñar slide deck comercial: value proposition, dolores, modelo y diferenciador PS</t>
-  </si>
-  <si>
-    <t>Slide deck comercial v1.0 listo para presentar a clientes nuevos</t>
-  </si>
-  <si>
-    <t>E2-011</t>
-  </si>
-  <si>
-    <t>039. Diseñar slide deck para equipo de operación: qué cambia, roles y proceso de recepción</t>
-  </si>
-  <si>
-    <t>Slide deck de operación v1.0: cómo recibir y ejecutar el servicio</t>
-  </si>
-  <si>
-    <t>E2-013</t>
-  </si>
-  <si>
-    <t>040. Validación y feedback de las definiciones del servicio con comercial y DMs</t>
-  </si>
-  <si>
-    <t>Acta de validación y ajustes acordados con equipo comercial</t>
-  </si>
-  <si>
-    <t>E2-014</t>
-  </si>
-  <si>
-    <t>041. Validar modelo operativo con líderes de operación (trenes)</t>
-  </si>
-  <si>
-    <t>Acta de validación con líderes de operación y ajustes incorporados</t>
-  </si>
-  <si>
-    <t>E2-HU004</t>
-  </si>
-  <si>
-    <t>E2 [HU-004] - Piloto de herramientas y agentes para las mesas de servicio (reuso o construcción nuevas)</t>
-  </si>
-  <si>
-    <t>E2-019</t>
-  </si>
-  <si>
-    <t>042. Evaluar y seleccionar herramienta estándar PS para gestión de tickets</t>
-  </si>
-  <si>
-    <t>Decisión documentada: herramienta estándar PS seleccionada con criterios y justificación</t>
-  </si>
-  <si>
-    <t>E2-020</t>
-  </si>
-  <si>
-    <t>043. Identificar y priorizar automatizaciones: agentes IA y robots RPA para el servicio</t>
-  </si>
-  <si>
-    <t>Inventario priorizado de automatizaciones: agentes y RPA con caso de uso por nivel</t>
-  </si>
-  <si>
-    <t>E2-021</t>
-  </si>
-  <si>
-    <t>044. Diseñar e iniciar piloto de herramientas/agentes para las mesas (reuso o construcción nueva)</t>
-  </si>
-  <si>
-    <t>Piloto de herramientas/agentes diseñado y en ejecución con resultados preliminares</t>
-  </si>
-  <si>
-    <t>E2-022</t>
-  </si>
-  <si>
-    <t>045. Diseñar estructura de reportes ejecutivos y dashboard de operación para PS</t>
-  </si>
-  <si>
-    <t>Diseño del dashboard ejecutivo interno PS: métricas, frecuencia y responsables</t>
-  </si>
-  <si>
-    <t>E2-024</t>
-  </si>
-  <si>
-    <t>046. Definir lineamientos de gestión de conocimiento y límites del servicio por tipo de mesa</t>
-  </si>
-  <si>
-    <t>Lineamiento de límites del servicio + guía de gestión del conocimiento por tipo de mesa</t>
-  </si>
-  <si>
-    <t>Total horas estimadas (Agosto)</t>
-  </si>
-  <si>
-    <t>SEPTIEMBRE · Productización del Servicio → Piloto Cliente Nuevo → Lanzamiento servicio nuevo</t>
-  </si>
-  <si>
-    <t>E3-HU001</t>
-  </si>
-  <si>
-    <t>E3 [HU-001] - Productización del servicio: colaterales comerciales y de operación</t>
-  </si>
-  <si>
-    <t>Productización del Servicio</t>
-  </si>
-  <si>
     <t>E3-001</t>
   </si>
   <si>
-    <t>047. Construir kit comercial v1.0: propuestas tipo, contratos, colaterales de venta y calculadora del servicio</t>
+    <t>047. Construir kit comercial v1.0: propuestas tipo, contratos y colaterales de venta</t>
   </si>
   <si>
     <t>Kit comercial v1.0: propuestas tipo, contratos y colaterales listos para usar</t>
@@ -618,16 +618,16 @@
     <t>E3-003</t>
   </si>
   <si>
-    <t>049. Construir calculadora del servicio v1.0: plantilla de estimación por mesa con parámetros</t>
-  </si>
-  <si>
-    <t>Calculadora del servicio v1.0 con parámetros clave (FTE, GAP, horas, costo por ticket)</t>
+    <t>049. Construir calculadora del servicio v1.0: plantilla de estimación por mesa</t>
+  </si>
+  <si>
+    <t>Calculadora del servicio v1.0 con parámetros clave (FTE, GAP, horas, costo/ticket)</t>
   </si>
   <si>
     <t>E3-004</t>
   </si>
   <si>
-    <t>050. Diseñar estrategia de transferencia de conocimiento comercial (pitch, calculadora, colaterales)</t>
+    <t>050. Diseñar estrategia de transferencia de conocimiento comercial</t>
   </si>
   <si>
     <t>Plan de habilitación comercial: pitch, calculadora y colaterales dominados</t>
@@ -636,7 +636,7 @@
     <t>E3-005</t>
   </si>
   <si>
-    <t>051. Diseñar estrategia de transferencia de conocimiento delivery/operación (playbook, RACI, ANS)</t>
+    <t>051. Diseñar estrategia de transferencia de conocimiento delivery / operación</t>
   </si>
   <si>
     <t>Plan de habilitación operación: playbook, RACI y proceso de recepción del servicio</t>
@@ -705,7 +705,7 @@
     <t>E2-017</t>
   </si>
   <si>
-    <t>057. Ejecutar pre-piloto interno con equipo PS: validar flujo del servicio extremo a extremo</t>
+    <t>057. Ejecutar pre-piloto interno con equipo PersonalSoft: validar flujo del servicio E2E</t>
   </si>
   <si>
     <t>Resultados del pre-piloto interno: flujo validado con ajustes documentados</t>
@@ -732,7 +732,7 @@
     <t>E3-HU003</t>
   </si>
   <si>
-    <t>E3 [HU-003] - Lanzamiento oficial del servicio nuevo a clientes</t>
+    <t>E3 [HU-003] - Productización final: modelo de costos y colaterales del servicio nuevo</t>
   </si>
   <si>
     <t>Lanzamiento servicio nuevo</t>
@@ -744,7 +744,7 @@
     <t>060. Definir modelo de costos del servicio: estructura, márgenes y modelo de cobro</t>
   </si>
   <si>
-    <t>Modelo de costos del servicio documentado con estructura de márgenes y opciones de cobro</t>
+    <t>Modelo de costos documentado con estructura de márgenes y opciones de cobro</t>
   </si>
   <si>
     <t>E3-011</t>
@@ -780,70 +780,94 @@
     <t>064. Inicio actualización del servicio en la herramienta de procesos de PersonalSoft</t>
   </si>
   <si>
-    <t>Servicio actualizado en herramienta de procesos PS con versión aprobada</t>
+    <t>Inicio de actualización en herramienta de procesos PS (completar en Octubre)</t>
+  </si>
+  <si>
+    <t>Total horas estimadas (Septiembre)</t>
+  </si>
+  <si>
+    <t>OCTUBRE · Lanzamiento oficial → Actualización procesos PS → Priorización transición → Transición Wave 1 · Wave 2 en standby Nov/Dic</t>
+  </si>
+  <si>
+    <t>E3-HU004</t>
+  </si>
+  <si>
+    <t>E3 [HU-004] - Lanzamiento oficial del servicio y actualización de procesos internos PS</t>
   </si>
   <si>
     <t>E3-015</t>
   </si>
   <si>
-    <t>065. Lanzamiento oficial interno: comunicar y publicar el servicio estandarizado</t>
+    <t>065. Finalizar actualización del servicio en la herramienta de procesos de PersonalSoft</t>
+  </si>
+  <si>
+    <t>Servicio completamente actualizado en herramienta de procesos PS con versión aprobada</t>
+  </si>
+  <si>
+    <t>E3-NEW1</t>
+  </si>
+  <si>
+    <t>066. Actualizar procesos operativos internos de PersonalSoft para la nueva operación del servicio</t>
+  </si>
+  <si>
+    <t>Procesos internos PS actualizados: operación, gobierno, escalamiento y reporting del servicio nuevo</t>
+  </si>
+  <si>
+    <t>E3-016</t>
+  </si>
+  <si>
+    <t>067. Lanzamiento oficial interno: comunicar y publicar el servicio estandarizado</t>
   </si>
   <si>
     <t>Lanzamiento oficial ejecutado: servicio publicado y comunicado internamente</t>
   </si>
   <si>
-    <t>E3-HU004</t>
-  </si>
-  <si>
-    <t>E3 [HU-004] - Priorización y planificación de la transición de clientes existentes</t>
-  </si>
-  <si>
-    <t>E3-016</t>
-  </si>
-  <si>
-    <t>066. Priorizar las mesas a transicionar: criterios de selección y orden de olas</t>
+    <t>E3-HU005</t>
+  </si>
+  <si>
+    <t>E3 [HU-005] - Priorización y planificación de la transición de clientes existentes</t>
+  </si>
+  <si>
+    <t>Transición Clientes Existentes</t>
+  </si>
+  <si>
+    <t>E3-017</t>
+  </si>
+  <si>
+    <t>068. Priorizar las mesas a transicionar: criterios de selección y orden de olas</t>
   </si>
   <si>
     <t>Matriz de priorización de mesas a transicionar con criterios y orden de olas</t>
   </si>
   <si>
-    <t>E3-017</t>
-  </si>
-  <si>
-    <t>067. Iniciar creación del plan de transición para clientes actuales (Wave 1)</t>
+    <t>E3-018</t>
+  </si>
+  <si>
+    <t>069. Iniciar creación del plan de transición para clientes actuales (Wave 1)</t>
   </si>
   <si>
     <t>Plan de transición Wave 1 v1.0: fases, actividades, responsables y cronograma</t>
   </si>
   <si>
-    <t>E3-018</t>
-  </si>
-  <si>
-    <t>068. Identificar costos de transición al servicio nuevo por cliente</t>
-  </si>
-  <si>
-    <t>Matriz de costos de transición por cliente: costos actuales vs costo del nuevo modelo</t>
-  </si>
-  <si>
-    <t>Total horas estimadas (Septiembre)</t>
-  </si>
-  <si>
-    <t>OCTUBRE · Transición Clientes Existentes (Wave 1 + Wave 2) + Habilitaciones + Evolución continua del servicio</t>
+    <t>E3-019</t>
+  </si>
+  <si>
+    <t>070. Identificar costos de transición al servicio nuevo por cliente</t>
+  </si>
+  <si>
+    <t>Matriz de costos de transición por cliente: costos actuales vs nuevo modelo</t>
   </si>
   <si>
     <t>E4-HU001</t>
   </si>
   <si>
-    <t>E4 [HU-001] - Inicio habilitación clientes actuales Wave 1</t>
-  </si>
-  <si>
-    <t>Transición Clientes Existentes</t>
+    <t>E4 [HU-001] - Habilitación y transición operativa Wave 1</t>
   </si>
   <si>
     <t>E4-001</t>
   </si>
   <si>
-    <t>069. Ejecutar habilitación equipo operación Wave 1: inducción y capacitación funcional del nuevo modelo</t>
+    <t>071. Ejecutar habilitación equipo operación Wave 1: inducción y capacitación funcional</t>
   </si>
   <si>
     <t>Equipo operación Wave 1 habilitado: inducción ejecutada y KEDB Wave 1 montado</t>
@@ -852,7 +876,7 @@
     <t>E4-002</t>
   </si>
   <si>
-    <t>070. Ejecutar habilitación equipo comercial Wave 1: pitch, calculadora y colaterales</t>
+    <t>072. Ejecutar habilitación equipo comercial Wave 1: pitch, calculadora y colaterales</t>
   </si>
   <si>
     <t>Equipo comercial Wave 1 habilitado: pitch y calculadora dominados</t>
@@ -861,73 +885,121 @@
     <t>E4-003</t>
   </si>
   <si>
-    <t>071. Presentar el nuevo modelo al cliente Wave 1 y gestionar acuerdos contractuales</t>
+    <t>073. Presentar el nuevo modelo al cliente Wave 1 y gestionar acuerdos contractuales</t>
   </si>
   <si>
     <t>Acuerdo contractual Wave 1 firmado con condiciones del nuevo modelo</t>
   </si>
   <si>
+    <t>E4-004</t>
+  </si>
+  <si>
+    <t>074. Ejecutar transición operativa Wave 1 — mesa 1 al nuevo modelo estandarizado</t>
+  </si>
+  <si>
+    <t>Acta de arranque mesa 1 Wave 1: ANS activos, equipo habilitado y operación iniciada</t>
+  </si>
+  <si>
+    <t>E4-005</t>
+  </si>
+  <si>
+    <t>075. Ejecutar transición operativa Wave 1 — mesa 2 al nuevo modelo estandarizado</t>
+  </si>
+  <si>
+    <t>Acta de arranque mesa 2 Wave 1: ANS activos y operación iniciada</t>
+  </si>
+  <si>
+    <t>E4-006</t>
+  </si>
+  <si>
+    <t>076. Validar ANS, KPIs y reportes Wave 1 en operación real — primeras 2 semanas</t>
+  </si>
+  <si>
+    <t>Reporte de primeras 2 semanas Wave 1: ANS cumplidos, KPIs y hallazgos</t>
+  </si>
+  <si>
+    <t>E4-007</t>
+  </si>
+  <si>
+    <t>077. Medir primera ronda CSAT/XLA Wave 1 y registrar feedback del cliente</t>
+  </si>
+  <si>
+    <t>Primera medición CSAT/XLA Wave 1 con informe de feedback del cliente</t>
+  </si>
+  <si>
     <t>E4-HU002</t>
   </si>
   <si>
-    <t>E4 [HU-002] - Transición operativa Wave 1</t>
-  </si>
-  <si>
-    <t>E4-004</t>
-  </si>
-  <si>
-    <t>072. Ejecutar transición operativa Wave 1 — mesa 1 al nuevo modelo estandarizado</t>
-  </si>
-  <si>
-    <t>Acta de arranque mesa 1 Wave 1: ANS activos, equipo habilitado y operación iniciada</t>
-  </si>
-  <si>
-    <t>E4-005</t>
-  </si>
-  <si>
-    <t>073. Ejecutar transición operativa Wave 1 — mesa 2 al nuevo modelo estandarizado</t>
-  </si>
-  <si>
-    <t>Acta de arranque mesa 2 Wave 1: ANS activos y operación iniciada</t>
-  </si>
-  <si>
-    <t>E4-006</t>
-  </si>
-  <si>
-    <t>074. Validar ANS, KPIs y reportes Wave 1 en operación real — primeras 2 semanas</t>
-  </si>
-  <si>
-    <t>Reporte de primeras 2 semanas Wave 1: ANS cumplidos, KPIs y hallazgos</t>
-  </si>
-  <si>
-    <t>E4-007</t>
-  </si>
-  <si>
-    <t>075. Medir primera ronda CSAT/XLA Wave 1 y registrar feedback del cliente</t>
-  </si>
-  <si>
-    <t>Primera medición CSAT/XLA Wave 1 con informe de feedback del cliente</t>
+    <t>E4 [HU-002] - Finalización de colaterales, lecciones aprendidas y evolución continua</t>
+  </si>
+  <si>
+    <t>E4-013</t>
+  </si>
+  <si>
+    <t>078. Finalizar colaterales equipo comercial y operación (contratos, plantillas, presentaciones)</t>
+  </si>
+  <si>
+    <t>Paquete final comercial y operativo completo y aprobado</t>
+  </si>
+  <si>
+    <t>E4-014</t>
+  </si>
+  <si>
+    <t>079. Identificar lecciones aprendidas de las 4 fases e incorporar al modelo v2.0</t>
+  </si>
+  <si>
+    <t>Modelo del servicio v2.0 con lecciones aprendidas incorporadas</t>
+  </si>
+  <si>
+    <t>E4-015</t>
+  </si>
+  <si>
+    <t>080. Identificar automatizaciones prioritarias y definir backlog de evolución</t>
+  </si>
+  <si>
+    <t>Backlog de evolución v1.0: automatizaciones, agentes IA y mejoras priorizadas</t>
+  </si>
+  <si>
+    <t>E4-016</t>
+  </si>
+  <si>
+    <t>081. Definir estrategia de expansión: nuevos clientes, Centro América y versión Alfa</t>
+  </si>
+  <si>
+    <t>Estrategia de expansión documentada con propuesta para nuevos mercados</t>
+  </si>
+  <si>
+    <t>E4-017</t>
+  </si>
+  <si>
+    <t>082. Validar y evolucionar el dashboard ejecutivo interno PersonalSoft</t>
+  </si>
+  <si>
+    <t>Dashboard ejecutivo PS v2.0 validado con evolución Wave 1</t>
   </si>
   <si>
     <t>E4-HU003</t>
   </si>
   <si>
-    <t>E4 [HU-003] - Transición clientes existentes Wave 2 + preparación</t>
+    <t>E4 [HU-003] - Transición Wave 2 — STANDBY: ejecutar después de Wave 1 (Nov/Dic)</t>
+  </si>
+  <si>
+    <t>Standby - Nov/Dic</t>
   </si>
   <si>
     <t>E4-008</t>
   </si>
   <si>
-    <t>076. Definir plan de transición Wave 2: clientes, fases y cronograma</t>
-  </si>
-  <si>
-    <t>Plan de transición Wave 2: clientes priorizados, fases y cronograma aprobado</t>
+    <t>083. Definir plan de transición Wave 2: clientes, fases y cronograma [→ Nov/Dic]</t>
+  </si>
+  <si>
+    <t>Plan de transición Wave 2 aprobado [pendiente resultados Wave 1]</t>
   </si>
   <si>
     <t>E4-009</t>
   </si>
   <si>
-    <t>077. Ejecutar habilitación equipo operación Wave 2</t>
+    <t>084. Ejecutar habilitación equipo operación Wave 2 [→ Nov/Dic]</t>
   </si>
   <si>
     <t>Equipo operación Wave 2 habilitado y KEDB Wave 2 montado</t>
@@ -936,79 +1008,28 @@
     <t>E4-010</t>
   </si>
   <si>
-    <t>078. Ejecutar transición operativa mesas Wave 2 al nuevo modelo</t>
-  </si>
-  <si>
-    <t>Actas de arranque Wave 2: mesas operando con nuevo modelo estandarizado</t>
+    <t>085. Ejecutar transición operativa mesas Wave 2 [→ Nov/Dic]</t>
+  </si>
+  <si>
+    <t>Actas de arranque Wave 2: mesas operando con nuevo modelo</t>
   </si>
   <si>
     <t>E4-011</t>
   </si>
   <si>
-    <t>079. Validar ANS, KPIs y reportes Wave 2 — primeras 2 semanas</t>
-  </si>
-  <si>
-    <t>Reporte primeras 2 semanas Wave 2: ANS, KPIs y hallazgos documentados</t>
+    <t>086. Validar ANS, KPIs y reportes Wave 2 — primeras 2 semanas [→ Nov/Dic]</t>
+  </si>
+  <si>
+    <t>Reporte Wave 2: ANS, KPIs y hallazgos documentados</t>
   </si>
   <si>
     <t>E4-012</t>
   </si>
   <si>
-    <t>080. Medir CSAT/XLA Wave 2 y registrar feedback del cliente</t>
+    <t>087. Medir CSAT/XLA Wave 2 y registrar feedback [→ Nov/Dic]</t>
   </si>
   <si>
     <t>Primera medición CSAT/XLA Wave 2 con informe de feedback</t>
-  </si>
-  <si>
-    <t>E4-HU004</t>
-  </si>
-  <si>
-    <t>E4 [HU-004] - Finalización de colaterales, evolución continua y expansión</t>
-  </si>
-  <si>
-    <t>E4-013</t>
-  </si>
-  <si>
-    <t>081. Finalizar colaterales equipo comercial y operación (contratos, plantillas, presentaciones, propuestas)</t>
-  </si>
-  <si>
-    <t>Paquete final comercial y operativo completo y aprobado</t>
-  </si>
-  <si>
-    <t>E4-014</t>
-  </si>
-  <si>
-    <t>082. Identificar lecciones aprendidas de las 4 fases e incorporar al modelo v2.0</t>
-  </si>
-  <si>
-    <t>Modelo del servicio v2.0 con lecciones aprendidas de las 4 fases incorporadas</t>
-  </si>
-  <si>
-    <t>E4-015</t>
-  </si>
-  <si>
-    <t>083. Identificar automatizaciones prioritarias y definir backlog de evolución del servicio</t>
-  </si>
-  <si>
-    <t>Backlog de evolución v1.0: automatizaciones, agentes IA y mejoras priorizadas</t>
-  </si>
-  <si>
-    <t>E4-016</t>
-  </si>
-  <si>
-    <t>084. Definir estrategia de expansión: nuevos clientes, Centro América y versión Alfa</t>
-  </si>
-  <si>
-    <t>Estrategia de expansión documentada con propuesta para nuevos mercados</t>
-  </si>
-  <si>
-    <t>E4-017</t>
-  </si>
-  <si>
-    <t>085. Validar y evolucionar el dashboard ejecutivo interno PersonalSoft</t>
-  </si>
-  <si>
-    <t>Dashboard ejecutivo PS v2.0 validado con evolución Wave 1 vs Wave 2</t>
   </si>
   <si>
     <t>Total horas estimadas (Octubre)</t>
@@ -1453,7 +1474,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1541,6 +1562,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF888888"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
@@ -1579,7 +1607,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1648,8 +1676,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFEBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
-        <bgColor rgb="FF969696"/>
+        <bgColor rgb="FF888888"/>
       </patternFill>
     </fill>
   </fills>
@@ -1834,13 +1868,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1852,11 +1886,17 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1865,15 +1905,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1888,7 +1934,13 @@
     <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1909,13 +1961,13 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1940,21 +1992,21 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
@@ -1965,7 +2017,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -1990,7 +2042,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFD3D1C7"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF888888"/>
       <rgbColor rgb="FF5B9BD5"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
@@ -2012,7 +2064,7 @@
       <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFFAEEDA"/>
       <rgbColor rgb="FFE6F1FB"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFEBF3FB"/>
       <rgbColor rgb="FFFAECE7"/>
       <rgbColor rgb="FF3366FF"/>
@@ -2063,9 +2115,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>236880</xdr:colOff>
+      <xdr:colOff>236520</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>132480</xdr:rowOff>
+      <xdr:rowOff>132120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2085,7 +2137,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6092640" y="419040"/>
-          <a:ext cx="6310800" cy="3151800"/>
+          <a:ext cx="6310440" cy="3151440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2465,36 +2517,36 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="56" t="s">
-        <v>325</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>455</v>
+      <c r="B1" s="62" t="s">
+        <v>332</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C2" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2505,73 +2557,73 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B7" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="B8" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C8" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B9" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C9" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="B10" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C10" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -2596,12 +2648,12 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.54296875" customWidth="1"/>
-    <col min="2" max="2" width="73.453125" customWidth="1"/>
+    <col min="2" max="2" width="69.7265625" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" style="7" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="16" style="7" customWidth="1"/>
-    <col min="6" max="6" width="74.08984375" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="6" max="6" width="73.81640625" customWidth="1"/>
+    <col min="7" max="7" width="18.08984375" customWidth="1"/>
     <col min="8" max="8" width="60" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2624,593 +2676,593 @@
       <c r="F1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="11">
+      <c r="D4" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="13">
         <v>8</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="11">
+      <c r="C5" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="13">
         <v>1</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="11">
+      <c r="C6" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="13">
         <v>1</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="11">
+      <c r="C7" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="13">
         <v>1</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="11">
+      <c r="C8" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="13">
         <v>1</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="11">
+      <c r="C9" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="13">
         <v>1</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="11">
+      <c r="C10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="13">
         <v>1</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="11">
+      <c r="C11" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="13">
         <v>1</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="11">
+      <c r="C12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="13">
         <v>1</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="11">
+      <c r="C13" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="13">
         <v>1</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="11">
+      <c r="C14" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="13">
         <v>12</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="11">
+      <c r="C15" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="13">
         <v>2</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10" t="s">
+      <c r="E16" s="10"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="11">
+      <c r="C17" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="13">
         <v>2</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="11">
+      <c r="C18" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="13">
         <v>1</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="11">
+      <c r="C19" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="13">
         <v>1</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="11">
+      <c r="C20" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="13">
         <v>5</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10" t="s">
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="12" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="11">
+      <c r="C22" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="13">
         <v>16</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
+    <row r="23" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="C23" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="13">
         <v>8</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
+    <row r="24" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="11">
+      <c r="C24" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="13">
         <v>12</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
+    <row r="25" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="11">
+      <c r="C25" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="13">
         <v>24</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
+    <row r="26" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10" t="s">
+      <c r="E26" s="10"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="12" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="11" t="s">
+    <row r="27" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="11">
+      <c r="C27" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="13">
         <v>3</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="16" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
+      <c r="A28" s="17"/>
+      <c r="B28" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="15">
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="17">
         <f>SUM(E3:E27)</f>
         <v>103</v>
       </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3223,16 +3275,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="82" customWidth="1"/>
+    <col min="2" max="2" width="81.08984375" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="16" style="7" customWidth="1"/>
     <col min="6" max="6" width="65" style="4" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="7" max="7" width="28.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -3259,454 +3311,431 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="11">
+      <c r="C4" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="13">
         <v>7</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="20" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="11">
+      <c r="C5" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="13">
         <v>8</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="20" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="11">
+      <c r="C6" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="13">
         <v>8</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="20" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="11">
+      <c r="C7" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="13">
         <v>4</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="20" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="11">
+      <c r="C8" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="13">
         <v>5</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="20" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="11">
+      <c r="C9" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="13">
         <v>12</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="11">
+      <c r="C10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="13">
+        <v>8</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="13">
+        <v>6</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="13">
+        <v>3</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="13">
+        <v>3</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="13">
+        <v>8</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="13">
         <v>5</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="G10" s="14" t="s">
+      <c r="F17" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" s="20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10" t="s">
+    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="13">
+        <v>6</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G18" s="20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="11">
-        <v>8</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="G12" s="14" t="s">
+    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="13">
+        <v>6</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="G19" s="20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="11">
-        <v>6</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="G13" s="14" t="s">
+    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="13">
+        <v>4</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="G20" s="20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="11">
-        <v>3</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="11">
-        <v>3</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="11">
-        <v>8</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="11">
-        <v>5</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="11">
-        <v>6</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="11">
-        <v>6</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="11">
-        <v>4</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="15"/>
-      <c r="B22" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="15">
-        <f>SUM(E3:E21)</f>
-        <v>98</v>
-      </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="17">
+        <f>SUM(E3:E20)</f>
+        <v>93</v>
+      </c>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3719,16 +3748,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
     <col min="2" max="2" width="82" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="4" max="4" width="23.36328125" customWidth="1"/>
     <col min="5" max="5" width="16" style="7" customWidth="1"/>
     <col min="6" max="6" width="65" style="4" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="7" max="7" width="26.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -3755,630 +3784,542 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B4" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C4" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="13">
+        <v>5</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="13">
+        <v>8</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="13">
+        <v>8</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="13">
+        <v>8</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="13">
+        <v>8</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="13">
+        <v>8</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="11">
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="13">
+        <v>6</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="13">
+        <v>6</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="13">
         <v>8</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="11">
+      <c r="F13" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="13">
+        <v>12</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="13">
+        <v>2</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="13">
+        <v>10</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="13">
         <v>8</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="11">
+      <c r="F18" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="13">
+        <v>6</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="13">
         <v>8</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="11">
-        <v>8</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="11">
-        <v>8</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="11">
+      <c r="F21" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="13">
+        <v>5</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="13">
         <v>6</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="11">
+      <c r="F23" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="13">
         <v>6</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="11">
-        <v>8</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="11">
-        <v>12</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="11">
-        <v>2</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="11">
-        <v>10</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="11">
-        <v>8</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="11">
-        <v>6</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10" t="s">
+      <c r="F24" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="G24" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="11">
-        <v>8</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="G20" s="19" t="s">
+    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="13">
+        <v>4</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="G25" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="11">
-        <v>5</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="11">
-        <v>6</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="11">
-        <v>6</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="11">
-        <v>4</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="17"/>
+      <c r="B26" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="11">
-        <v>3</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="11">
-        <v>3</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="11">
-        <v>6</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="11">
-        <v>5</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="15"/>
-      <c r="B30" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="15">
-        <f>SUM(E3:E29)</f>
-        <v>144</v>
-      </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="17">
+        <f>SUM(E3:E25)</f>
+        <v>132</v>
+      </c>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4391,16 +4332,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="82" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="77.6328125" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="16" style="7" customWidth="1"/>
     <col min="6" max="6" width="65" style="4" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -4427,496 +4368,653 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="13">
+        <v>6</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="13">
+        <v>8</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="13">
+        <v>3</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B8" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C8" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="13">
+        <v>3</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="13">
+        <v>6</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="13">
+        <v>5</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="11">
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="13">
         <v>6</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="11">
+      <c r="F12" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="13">
         <v>4</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="11">
+      <c r="F13" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="13">
         <v>4</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="F14" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="13">
+        <v>6</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="13">
+        <v>6</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="13">
+        <v>5</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="13">
+        <v>3</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="11">
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="13">
+        <v>8</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="13">
+        <v>4</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="13">
+        <v>5</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="13">
+        <v>5</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="13">
+        <v>4</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="25">
+        <v>5</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="25" t="s">
+        <v>317</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="25">
         <v>6</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="11">
-        <v>6</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="11">
+      <c r="F27" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="25">
+        <v>8</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="25">
         <v>5</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="11">
+      <c r="F29" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="25">
         <v>3</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="11">
-        <v>5</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="11">
-        <v>6</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="11">
-        <v>8</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="11">
-        <v>5</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="11">
-        <v>3</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="11">
-        <v>8</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="11">
-        <v>4</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
+      <c r="F30" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="G30" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="11">
-        <v>5</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="11">
-        <v>5</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="11">
-        <v>4</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="15">
-        <f>SUM(E3:E23)</f>
-        <v>87</v>
-      </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="17"/>
+      <c r="B31" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="17">
+        <f>SUM(E3:E30)</f>
+        <v>118</v>
+      </c>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4941,555 +5039,555 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="A1" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
     </row>
     <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>330</v>
+      <c r="A4" s="27" t="s">
+        <v>332</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>333</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>331</v>
-      </c>
-      <c r="B5" s="23">
+      <c r="A5" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="B5" s="29">
         <f>Julio!E28</f>
         <v>103</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="29">
         <v>113.64</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="29">
         <f>B5-C5</f>
         <v>-10.64</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="30">
         <f>IFERROR(B5/C5,0)</f>
         <v>0.90637099612812388</v>
       </c>
-      <c r="F5" s="25" t="s">
-        <v>332</v>
+      <c r="F5" s="31" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="27">
-        <f>Agosto!E22</f>
-        <v>98</v>
-      </c>
-      <c r="C6" s="27">
+      <c r="B6" s="33">
+        <f>Agosto!E21</f>
+        <v>93</v>
+      </c>
+      <c r="C6" s="33">
         <v>151.88</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="33">
         <f>B6-C6</f>
-        <v>-53.879999999999995</v>
-      </c>
-      <c r="E6" s="28">
+        <v>-58.879999999999995</v>
+      </c>
+      <c r="E6" s="34">
         <f>IFERROR(B6/C6,0)</f>
-        <v>0.64524624703713462</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>333</v>
+        <v>0.61232552014748487</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="27">
-        <f>Septiembre!E30</f>
-        <v>144</v>
-      </c>
-      <c r="C7" s="27">
+      <c r="B7" s="33">
+        <f>Septiembre!E27</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="33">
         <v>164.5</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="33">
         <f>B7-C7</f>
-        <v>-20.5</v>
-      </c>
-      <c r="E7" s="28">
+        <v>-164.5</v>
+      </c>
+      <c r="E7" s="34">
         <f>IFERROR(B7/C7,0)</f>
-        <v>0.87537993920972645</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>334</v>
+        <v>0</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="B8" s="27">
-        <f>Octubre!E24</f>
-        <v>87</v>
-      </c>
-      <c r="C8" s="27">
+      <c r="A8" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="B8" s="33">
+        <f>Octubre!E31</f>
+        <v>118</v>
+      </c>
+      <c r="C8" s="33">
         <v>220.51</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="33">
         <f>B8-C8</f>
-        <v>-133.51</v>
-      </c>
-      <c r="E8" s="28">
+        <v>-102.50999999999999</v>
+      </c>
+      <c r="E8" s="34">
         <f>IFERROR(B8/C8,0)</f>
-        <v>0.39453993016189742</v>
-      </c>
-      <c r="F8" s="29" t="s">
+        <v>0.53512312366786086</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="36" t="s">
+        <v>344</v>
+      </c>
+      <c r="B9" s="37">
+        <f>SUM(B5:B8)</f>
+        <v>314</v>
+      </c>
+      <c r="C9" s="37">
+        <v>650.53</v>
+      </c>
+      <c r="D9" s="37">
+        <f>B9-C9</f>
+        <v>-336.53</v>
+      </c>
+      <c r="E9" s="38">
+        <f>IFERROR(B9/C9,0)</f>
+        <v>0.48268335049882405</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="40" t="s">
+        <v>346</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>347</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>348</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="43" t="s">
+        <v>350</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>351</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="43" t="s">
+        <v>354</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>355</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="43" t="s">
+        <v>358</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>359</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>360</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="43" t="s">
+        <v>362</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>363</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>364</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="43" t="s">
+        <v>366</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>367</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>368</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="45" t="s">
+        <v>370</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="40" t="s">
+        <v>374</v>
+      </c>
+      <c r="B21" s="41" t="s">
+        <v>375</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="D21" s="41" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="B9" s="31">
-        <f>SUM(B5:B8)</f>
-        <v>432</v>
-      </c>
-      <c r="C9" s="31">
-        <v>650.53</v>
-      </c>
-      <c r="D9" s="31">
-        <f>B9-C9</f>
-        <v>-218.52999999999997</v>
-      </c>
-      <c r="E9" s="32">
-        <f>IFERROR(B9/C9,0)</f>
-        <v>0.66407390896653495</v>
-      </c>
-      <c r="F9" s="33" t="s">
+      <c r="E21" s="42" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="32" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="34" t="s">
-        <v>339</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="D12" s="36" t="s">
+      <c r="B22" s="44" t="s">
+        <v>378</v>
+      </c>
+      <c r="C22" s="48">
+        <v>28.88</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>381</v>
+      </c>
+      <c r="C23" s="48">
+        <v>8.75</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>384</v>
+      </c>
+      <c r="C24" s="48">
+        <v>7</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>386</v>
+      </c>
+      <c r="C25" s="48">
+        <v>23.25</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="32" t="s">
+        <v>388</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>389</v>
+      </c>
+      <c r="C26" s="48">
+        <v>13.13</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="C27" s="48">
+        <v>45.5</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>393</v>
+      </c>
+      <c r="C28" s="48">
+        <v>37.18</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="44" t="s">
+        <v>395</v>
+      </c>
+      <c r="C29" s="48">
+        <v>35</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="32" t="s">
+        <v>397</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>398</v>
+      </c>
+      <c r="C30" s="48">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="44" t="s">
+        <v>400</v>
+      </c>
+      <c r="C31" s="48">
+        <v>8.75</v>
+      </c>
+      <c r="D31" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="E31" s="35" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>402</v>
+      </c>
+      <c r="C32" s="48">
+        <v>24.5</v>
+      </c>
+      <c r="D32" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="E32" s="35" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>404</v>
+      </c>
+      <c r="C33" s="48">
+        <v>36.75</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>406</v>
+      </c>
+      <c r="C34" s="48">
+        <v>36.75</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="32" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="37" t="s">
-        <v>343</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>344</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>345</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="37" t="s">
-        <v>347</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>348</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>349</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>352</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>353</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>356</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>360</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="B18" s="40" t="s">
-        <v>364</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>365</v>
-      </c>
-      <c r="D18" s="41" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>368</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>369</v>
-      </c>
-      <c r="D21" s="35" t="s">
-        <v>329</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>371</v>
-      </c>
-      <c r="C22" s="42">
-        <v>28.88</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="B23" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="C23" s="42">
-        <v>8.75</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>375</v>
-      </c>
-      <c r="E23" s="29" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>377</v>
-      </c>
-      <c r="C24" s="42">
-        <v>7</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>375</v>
-      </c>
-      <c r="E24" s="29" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="B25" s="38" t="s">
+      <c r="B35" s="44" t="s">
+        <v>408</v>
+      </c>
+      <c r="C35" s="48">
+        <v>48.13</v>
+      </c>
+      <c r="D35" s="44" t="s">
         <v>379</v>
       </c>
-      <c r="C25" s="42">
-        <v>23.25</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="26" t="s">
-        <v>381</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>382</v>
-      </c>
-      <c r="C26" s="42">
-        <v>13.13</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E26" s="29" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>384</v>
-      </c>
-      <c r="C27" s="42">
-        <v>45.5</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="C28" s="42">
-        <v>37.18</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>375</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" s="38" t="s">
-        <v>388</v>
-      </c>
-      <c r="C29" s="42">
-        <v>35</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>375</v>
-      </c>
-      <c r="E29" s="29" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="26" t="s">
-        <v>390</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>391</v>
-      </c>
-      <c r="C30" s="42">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="38" t="s">
-        <v>393</v>
-      </c>
-      <c r="C31" s="42">
-        <v>8.75</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>375</v>
-      </c>
-      <c r="E31" s="29" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="C32" s="42">
-        <v>24.5</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E32" s="29" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="38" t="s">
-        <v>397</v>
-      </c>
-      <c r="C33" s="42">
-        <v>36.75</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" s="38" t="s">
-        <v>399</v>
-      </c>
-      <c r="C34" s="42">
-        <v>36.75</v>
-      </c>
-      <c r="D34" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E34" s="29" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="B35" s="38" t="s">
-        <v>401</v>
-      </c>
-      <c r="C35" s="42">
-        <v>48.13</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E35" s="29" t="s">
-        <v>402</v>
+      <c r="E35" s="35" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>403</v>
-      </c>
-      <c r="C36" s="42">
+      <c r="A36" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="B36" s="44" t="s">
+        <v>410</v>
+      </c>
+      <c r="C36" s="48">
         <v>172.38</v>
       </c>
-      <c r="D36" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E36" s="29" t="s">
-        <v>404</v>
+      <c r="D36" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="E36" s="35" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="43"/>
-      <c r="B37" s="40"/>
-      <c r="C37" s="44"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="41"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="47"/>
     </row>
     <row r="39" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="45" t="s">
-        <v>405</v>
-      </c>
-      <c r="B39" s="45" t="s">
-        <v>406</v>
-      </c>
-      <c r="C39" s="45" t="s">
-        <v>407</v>
-      </c>
-      <c r="D39" s="45" t="s">
-        <v>408</v>
-      </c>
-      <c r="E39" s="45" t="s">
-        <v>409</v>
-      </c>
-      <c r="F39" s="45" t="s">
-        <v>410</v>
+      <c r="A39" s="51" t="s">
+        <v>412</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>413</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>415</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>416</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -5517,263 +5615,263 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="B1" s="47" t="s">
-        <v>411</v>
-      </c>
-      <c r="C1" s="47" t="s">
-        <v>412</v>
-      </c>
-      <c r="D1" s="47" t="s">
-        <v>413</v>
-      </c>
-      <c r="E1" s="47" t="s">
-        <v>414</v>
-      </c>
-      <c r="F1" s="47" t="s">
-        <v>415</v>
-      </c>
-      <c r="G1" s="48" t="s">
-        <v>330</v>
+      <c r="A1" s="52" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>418</v>
+      </c>
+      <c r="C1" s="53" t="s">
+        <v>419</v>
+      </c>
+      <c r="D1" s="53" t="s">
+        <v>420</v>
+      </c>
+      <c r="E1" s="53" t="s">
+        <v>421</v>
+      </c>
+      <c r="F1" s="53" t="s">
+        <v>422</v>
+      </c>
+      <c r="G1" s="54" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="B2" s="27">
+      <c r="A2" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="B2" s="33">
         <f>Julio!E28</f>
         <v>103</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="33">
         <v>120</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="33">
         <f>B2-C2</f>
         <v>-17</v>
       </c>
-      <c r="E2" s="49" t="str">
+      <c r="E2" s="55" t="str">
         <f>IF(D2&lt;=0,"Sí","No")</f>
         <v>Sí</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="33">
         <f>IFERROR(B2/60,0)</f>
         <v>1.7166666666666666</v>
       </c>
-      <c r="G2" s="29" t="s">
-        <v>416</v>
+      <c r="G2" s="35" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="27">
-        <f>Agosto!E22</f>
-        <v>98</v>
-      </c>
-      <c r="C3" s="27">
+      <c r="B3" s="33">
+        <f>Agosto!E21</f>
+        <v>93</v>
+      </c>
+      <c r="C3" s="33">
         <v>120</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="33">
         <f>B3-C3</f>
-        <v>-22</v>
-      </c>
-      <c r="E3" s="49" t="str">
+        <v>-27</v>
+      </c>
+      <c r="E3" s="55" t="str">
         <f>IF(D3&lt;=0,"Sí","No")</f>
         <v>Sí</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="33">
         <f>IFERROR(B3/60,0)</f>
-        <v>1.6333333333333333</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>417</v>
+        <v>1.55</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="27">
-        <f>Septiembre!E30</f>
-        <v>144</v>
-      </c>
-      <c r="C4" s="27">
+      <c r="B4" s="33">
+        <f>Septiembre!E27</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="33">
         <v>120</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="33">
         <f>B4-C4</f>
-        <v>24</v>
-      </c>
-      <c r="E4" s="49" t="str">
+        <v>-120</v>
+      </c>
+      <c r="E4" s="55" t="str">
         <f>IF(D4&lt;=0,"Sí","No")</f>
-        <v>No</v>
-      </c>
-      <c r="F4" s="27">
+        <v>Sí</v>
+      </c>
+      <c r="F4" s="33">
         <f>IFERROR(B4/60,0)</f>
-        <v>2.4</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>418</v>
+        <v>0</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="B5" s="27">
-        <f>Octubre!E24</f>
-        <v>87</v>
-      </c>
-      <c r="C5" s="27">
+      <c r="A5" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="B5" s="33">
+        <f>Octubre!E31</f>
+        <v>118</v>
+      </c>
+      <c r="C5" s="33">
         <v>120</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="33">
         <f>B5-C5</f>
-        <v>-33</v>
-      </c>
-      <c r="E5" s="49" t="str">
+        <v>-2</v>
+      </c>
+      <c r="E5" s="55" t="str">
         <f>IF(D5&lt;=0,"Sí","No")</f>
         <v>Sí</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="33">
         <f>IFERROR(B5/60,0)</f>
-        <v>1.45</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>419</v>
+        <v>1.9666666666666666</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="B6" s="31">
+      <c r="A6" s="36" t="s">
+        <v>344</v>
+      </c>
+      <c r="B6" s="37">
         <f>SUM(B2:B5)</f>
-        <v>432</v>
-      </c>
-      <c r="C6" s="31">
+        <v>314</v>
+      </c>
+      <c r="C6" s="37">
         <f>SUM(C2:C5)</f>
         <v>480</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="37">
         <f>B6-C6</f>
-        <v>-48</v>
-      </c>
-      <c r="E6" s="50" t="str">
+        <v>-166</v>
+      </c>
+      <c r="E6" s="56" t="str">
         <f>IF(B6&lt;=C6,"Sí","No")</f>
         <v>Sí</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="37">
         <f>IFERROR(B6/60,0)</f>
-        <v>7.2</v>
-      </c>
-      <c r="G6" s="33"/>
+        <v>5.2333333333333334</v>
+      </c>
+      <c r="G6" s="39"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="51" t="s">
-        <v>420</v>
-      </c>
-      <c r="B9" s="51" t="s">
-        <v>421</v>
+      <c r="A9" s="57" t="s">
+        <v>427</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="52" t="s">
-        <v>422</v>
-      </c>
-      <c r="B10" s="53" t="s">
-        <v>423</v>
+      <c r="A10" s="58" t="s">
+        <v>429</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="52" t="s">
-        <v>424</v>
-      </c>
-      <c r="B11" s="53" t="s">
-        <v>425</v>
+      <c r="A11" s="58" t="s">
+        <v>431</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="52" t="s">
-        <v>426</v>
-      </c>
-      <c r="B12" s="53" t="s">
-        <v>427</v>
+      <c r="A12" s="58" t="s">
+        <v>433</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="52" t="s">
-        <v>428</v>
-      </c>
-      <c r="B13" s="53" t="s">
-        <v>429</v>
+      <c r="A13" s="58" t="s">
+        <v>435</v>
+      </c>
+      <c r="B13" s="59" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="54" t="s">
-        <v>430</v>
-      </c>
-      <c r="B14" s="55" t="s">
-        <v>431</v>
+      <c r="A14" s="60" t="s">
+        <v>437</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="51" t="s">
-        <v>432</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>434</v>
+      <c r="A17" s="57" t="s">
+        <v>439</v>
+      </c>
+      <c r="B17" s="57" t="s">
+        <v>440</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="52" t="s">
-        <v>435</v>
-      </c>
-      <c r="B18" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>437</v>
+      <c r="A18" s="58" t="s">
+        <v>442</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>443</v>
+      </c>
+      <c r="C18" s="59" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="52" t="s">
-        <v>438</v>
-      </c>
-      <c r="B19" s="53" t="s">
-        <v>439</v>
-      </c>
-      <c r="C19" s="53" t="s">
-        <v>440</v>
+      <c r="A19" s="58" t="s">
+        <v>445</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>446</v>
+      </c>
+      <c r="C19" s="59" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="52" t="s">
-        <v>441</v>
-      </c>
-      <c r="B20" s="53" t="s">
-        <v>442</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>443</v>
+      <c r="A20" s="58" t="s">
+        <v>448</v>
+      </c>
+      <c r="B20" s="59" t="s">
+        <v>449</v>
+      </c>
+      <c r="C20" s="59" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="54" t="s">
-        <v>444</v>
-      </c>
-      <c r="B21" s="55" t="s">
-        <v>445</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>446</v>
+      <c r="A21" s="60" t="s">
+        <v>451</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>452</v>
+      </c>
+      <c r="C21" s="61" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -5788,59 +5886,59 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="56" t="s">
-        <v>447</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>448</v>
+      <c r="A1" s="62" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B2" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B3" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B4" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B5" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B6" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>461</v>
+      </c>
+      <c r="B7" t="s">
         <v>454</v>
-      </c>
-      <c r="B7" t="s">
-        <v>447</v>
       </c>
     </row>
   </sheetData>
